--- a/src/main/resources/excel-templates/用户导入模板.xlsx
+++ b/src/main/resources/excel-templates/用户导入模板.xlsx
@@ -31,6 +31,30 @@
           </rPr>
           <t xml:space="preserve">必填且唯一
 </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>必填</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>必填</t>
         </r>
       </text>
     </comment>
@@ -247,18 +271,12 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.25"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -595,10 +613,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -607,16 +625,16 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -628,52 +646,52 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -682,16 +700,19 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -703,37 +724,34 @@
     <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -747,7 +765,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>

--- a/src/main/resources/excel-templates/用户导入模板.xlsx
+++ b/src/main/resources/excel-templates/用户导入模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25605" windowHeight="12345"/>
+    <workbookView windowWidth="28800" windowHeight="11940"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -66,7 +66,7 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>多个角色英文逗号(,)分割</t>
+          <t>角色编码，多个使用英文逗号(,)分割，例如：ADMIN,GUEST</t>
         </r>
       </text>
     </comment>
@@ -80,7 +80,7 @@
     <t>用户名</t>
   </si>
   <si>
-    <t>用户昵称</t>
+    <t>昵称</t>
   </si>
   <si>
     <t>性别</t>
@@ -92,7 +92,7 @@
     <t>邮箱</t>
   </si>
   <si>
-    <t>角色编码</t>
+    <t>角色</t>
   </si>
 </sst>
 </file>
